--- a/data/PACE_Department_Lookup.xlsx
+++ b/data/PACE_Department_Lookup.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
